--- a/PCB/PickAndPlace_PCB1_2026_08_11.xlsx
+++ b/PCB/PickAndPlace_PCB1_2026_08_11.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4150" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4218" uniqueCount="741">
   <si>
     <t>Designator</t>
   </si>
@@ -298,13 +298,13 @@
     <t>C2</t>
   </si>
   <si>
-    <t>64.925mm</t>
-  </si>
-  <si>
-    <t>-46.964mm</t>
-  </si>
-  <si>
-    <t>64.504mm</t>
+    <t>66.1mm</t>
+  </si>
+  <si>
+    <t>-47.7mm</t>
+  </si>
+  <si>
+    <t>65.68mm</t>
   </si>
   <si>
     <t>gge19</t>
@@ -370,13 +370,13 @@
     <t>C4</t>
   </si>
   <si>
-    <t>70.133mm</t>
-  </si>
-  <si>
-    <t>-50.215mm</t>
-  </si>
-  <si>
-    <t>-49.515mm</t>
+    <t>70.333mm</t>
+  </si>
+  <si>
+    <t>-52.415mm</t>
+  </si>
+  <si>
+    <t>-51.715mm</t>
   </si>
   <si>
     <t>gge23</t>
@@ -568,763 +568,763 @@
     <t>CONN-TH_XT30UPB-M</t>
   </si>
   <si>
-    <t>76.8mm</t>
+    <t>78.1mm</t>
+  </si>
+  <si>
+    <t>-41.6mm</t>
+  </si>
+  <si>
+    <t>-44.1mm</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>AMASS(艾迈斯)板载立式 航模锂电池控制器连接器插头 PCB板立式 公头XT30UPB-M.G.Y</t>
+  </si>
+  <si>
+    <t>AMASS(艾迈斯)</t>
+  </si>
+  <si>
+    <t>C428721</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/datasheet/XT30UPB-M/423831.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rated current:15A Rated voltage: colour:Yellow Connector type:Model aircraft plug contact resistance: interface form:Male insulating material: metal material:Gold plating </t>
+  </si>
+  <si>
+    <t>gge10</t>
+  </si>
+  <si>
+    <t>15A</t>
+  </si>
+  <si>
+    <t>Yellow</t>
+  </si>
+  <si>
+    <t>Model aircraft plug</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Gold plating</t>
+  </si>
+  <si>
+    <t>CN2</t>
+  </si>
+  <si>
+    <t>BM04B-SRSS-TB(LF)(SN)</t>
+  </si>
+  <si>
+    <t>CONN-SMD_BM04B-SRSS-TB</t>
+  </si>
+  <si>
+    <t>72.9mm</t>
+  </si>
+  <si>
+    <t>-70.6mm</t>
+  </si>
+  <si>
+    <t>74.4mm</t>
+  </si>
+  <si>
+    <t>-69.337mm</t>
+  </si>
+  <si>
+    <t>CONN-SMD_4P-L6.0-W2.9-H4.3-P1.0</t>
+  </si>
+  <si>
+    <t>1x4P 间距:1mm 立贴 系列:SR</t>
+  </si>
+  <si>
+    <t>JST</t>
+  </si>
+  <si>
+    <t>C160390</t>
+  </si>
+  <si>
+    <t>SMD,P=1mm</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/datasheet/BM04B-SRSS-TB(LF)(SN)/171770.html</t>
+  </si>
+  <si>
+    <t>Pins Structure:1x4P Pitch:1mm Mounting Type:Surface Mount,Vertical Reference Series:SR Number of Pins:4P Number of Rows:1 Number of PINs Per Row:4 Row Spacing:- Current Rating:1A Contact Material:Copper alloy Contact Plating:Tin Operating Temperature:-25℃</t>
+  </si>
+  <si>
+    <t>gge15</t>
+  </si>
+  <si>
+    <t>Auxiliary Solder Pin</t>
+  </si>
+  <si>
+    <t>-25℃~+85℃</t>
+  </si>
+  <si>
+    <t>1x4P</t>
+  </si>
+  <si>
+    <t>1mm</t>
+  </si>
+  <si>
+    <t>Surface Mount,Vertical</t>
+  </si>
+  <si>
+    <t>SR</t>
+  </si>
+  <si>
+    <t>4P</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1A</t>
+  </si>
+  <si>
+    <t>Copper alloy</t>
+  </si>
+  <si>
+    <t>Tin</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>UL94V-0</t>
+  </si>
+  <si>
+    <t>3.6mm</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>SS14_C112424</t>
+  </si>
+  <si>
+    <t>SMA_L4.4-W2.6-LS5.0-RD</t>
+  </si>
+  <si>
+    <t>49.396mm</t>
+  </si>
+  <si>
+    <t>-47.089mm</t>
+  </si>
+  <si>
+    <t>47.204mm</t>
+  </si>
+  <si>
+    <t>SS14</t>
+  </si>
+  <si>
+    <t>电压:40V 电流:1A</t>
+  </si>
+  <si>
+    <t>晶导微电子</t>
+  </si>
+  <si>
+    <t>C112424</t>
+  </si>
+  <si>
+    <t>SMA(DO-214AC)</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/datasheet/SS14/113656.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voltage - Forward(Vf@If):550mV@1A Voltage - DC Reverse(Vr):40V Current - Rectified:1A Reverse Leakage Current (Ir):300uA@40V Operating Junction Temperature Range:-55℃~+125℃ Operating Junction Temperature Range:-55℃~+125℃ Non-Repetitive Peak Forward Surge </t>
+  </si>
+  <si>
+    <t>gge27</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>2011-1X14G00SB</t>
+  </si>
+  <si>
+    <t>HDR-TH_14P-P2.54-V-M_4</t>
+  </si>
+  <si>
+    <t>60.311mm</t>
+  </si>
+  <si>
+    <t>-33.472mm</t>
+  </si>
+  <si>
+    <t>43.801mm</t>
+  </si>
+  <si>
+    <t>1x14P 间距:2.54mm 方针 直插</t>
+  </si>
+  <si>
+    <t>WingTAT(格林柏)</t>
+  </si>
+  <si>
+    <t>C49569637</t>
+  </si>
+  <si>
+    <t>插件,P=2.54mm</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/datasheet/2011-1X14G00SB/52123945.html</t>
+  </si>
+  <si>
+    <t>Pin Structure:1x14P Pitch:2.54mm Circluar Pins/Square Pins:Pin Header Mounting Type:Through Hole Number of Rows:1 Number of Pins:14P Current Rating:3A Voltage Rating (Max):600V Length of Mating Pin:6mm Insulation Height:2.5mm Length of End Connection Pin:</t>
+  </si>
+  <si>
+    <t>gge16</t>
+  </si>
+  <si>
+    <t>-40℃~+105℃</t>
+  </si>
+  <si>
+    <t>2.54mm</t>
+  </si>
+  <si>
+    <t>Through Hole</t>
+  </si>
+  <si>
+    <t>14P</t>
+  </si>
+  <si>
+    <t>3A</t>
+  </si>
+  <si>
+    <t>Brass</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>2.5mm</t>
+  </si>
+  <si>
+    <t>6mm</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>AOTA-B201610S3R3-101-T</t>
+  </si>
+  <si>
+    <t>IND-SMD_L2.0-W1.6_AOTA-B201610S3R3-101-T</t>
+  </si>
+  <si>
+    <t>50.875mm</t>
+  </si>
+  <si>
+    <t>-54.434mm</t>
+  </si>
+  <si>
+    <t>-54.426mm</t>
+  </si>
+  <si>
+    <t>-55.442mm</t>
+  </si>
+  <si>
+    <t>3.3uH</t>
+  </si>
+  <si>
+    <t>3.3uH 2.4A</t>
+  </si>
+  <si>
+    <t>ABRACON</t>
+  </si>
+  <si>
+    <t>C42411119</t>
+  </si>
+  <si>
+    <t>0806</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/datasheet/AOTA-B201610S3R3-101-T/44392932.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inductance:3.3uH Current Rating:2.1A Current - Saturation(Isat):2.4A DC Resistance(DCR):115mΩ Type:Molded Inductor </t>
+  </si>
+  <si>
+    <t>gge21</t>
+  </si>
+  <si>
+    <t>2.1A</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>RC0402FR-071KL</t>
+  </si>
+  <si>
+    <t>R0402</t>
+  </si>
+  <si>
+    <t>48.178mm</t>
+  </si>
+  <si>
+    <t>-51.811mm</t>
+  </si>
+  <si>
+    <t>-52.244mm</t>
+  </si>
+  <si>
+    <t>1kΩ</t>
+  </si>
+  <si>
+    <t>R0402_L1.0-W0.5-H0.4</t>
+  </si>
+  <si>
+    <t>厚膜电阻 1kΩ ±1% 62.5mW</t>
+  </si>
+  <si>
+    <t>C106235</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/datasheet/RC0402FR-071KL/107450.html</t>
+  </si>
+  <si>
+    <t>±1%</t>
+  </si>
+  <si>
+    <t>±100ppm/℃</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type:Thick Film Resistor Resistance:1kΩ Tolerance:±1% Tolerance:±1% Power(Watts):62.5mW Voltage-Supply(Max):50V Temperature Coefficient:±100ppm/℃ Temperature Coefficient:±100ppm/℃ Operating Temperature:-55℃~+155℃ Operating Temperature:-55℃~+155℃ </t>
+  </si>
+  <si>
+    <t>gge20</t>
+  </si>
+  <si>
+    <t>-55℃~+155℃</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>RC0402FR-0733RL</t>
+  </si>
+  <si>
+    <t>56.36mm</t>
+  </si>
+  <si>
+    <t>-73.599mm</t>
+  </si>
+  <si>
+    <t>55.927mm</t>
+  </si>
+  <si>
+    <t>33Ω</t>
+  </si>
+  <si>
+    <t>厚膜电阻 33Ω ±1% 62.5mW</t>
+  </si>
+  <si>
+    <t>C138002</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/datasheet/RC0402FR-0733RL/149318.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type:Thick Film Resistor Resistance:33Ω Tolerance:±1% Tolerance:±1% Power(Watts):62.5mW Voltage-Supply(Max):50V Temperature Coefficient:±100ppm/℃ Temperature Coefficient:±100ppm/℃ Operating Temperature:-55℃~+155℃ Operating Temperature:-55℃~+155℃ </t>
+  </si>
+  <si>
+    <t>gge25</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>FRC0402F1002TS</t>
+  </si>
+  <si>
+    <t>47.7mm</t>
+  </si>
+  <si>
+    <t>-75.8mm</t>
+  </si>
+  <si>
+    <t>48.133mm</t>
+  </si>
+  <si>
+    <t>10kΩ</t>
+  </si>
+  <si>
+    <t>10kΩ ±1% 62.5mW 厚膜电阻</t>
+  </si>
+  <si>
+    <t>FOJAN(富捷)</t>
+  </si>
+  <si>
+    <t>C2906861</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/datasheet/FRC0402F1002TS/3180374.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type:Thick Film Resistor Resistance:10kΩ Tolerance:±1% Tolerance:±1% Power(Watts):62.5mW Voltage-Supply(Max):50V Temperature Coefficient:±100ppm/℃ Temperature Coefficient:±100ppm/℃ Operating Temperature:-55℃~+155℃ Operating Temperature:-55℃~+155℃ </t>
+  </si>
+  <si>
+    <t>gge28</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>63.2mm</t>
+  </si>
+  <si>
+    <t>-70.3mm</t>
+  </si>
+  <si>
+    <t>-70.733mm</t>
+  </si>
+  <si>
+    <t>gge29</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>RC0402FR-0756KL</t>
+  </si>
+  <si>
+    <t>69.1mm</t>
+  </si>
+  <si>
+    <t>-64.5mm</t>
+  </si>
+  <si>
+    <t>69.533mm</t>
+  </si>
+  <si>
+    <t>56kΩ</t>
+  </si>
+  <si>
+    <t>厚膜电阻 56kΩ ±1% 62.5mW</t>
+  </si>
+  <si>
+    <t>C114756</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/datasheet/RC0402FR-0756KL/116000.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type:Thick Film Resistor Resistance:56kΩ Tolerance:±1% Tolerance:±1% Power(Watts):62.5mW Voltage-Supply(Max):50V Temperature Coefficient:±100ppm/℃ Temperature Coefficient:±100ppm/℃ Operating Temperature:-55℃~+155℃ Operating Temperature:-55℃~+155℃ </t>
+  </si>
+  <si>
+    <t>gge48</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>0402WGF1022TCE</t>
+  </si>
+  <si>
+    <t>48.3mm</t>
+  </si>
+  <si>
+    <t>-60.4mm</t>
+  </si>
+  <si>
+    <t>48.733mm</t>
+  </si>
+  <si>
+    <t>10.2kΩ</t>
+  </si>
+  <si>
+    <t>10.2kΩ ±1% 62.5mW 厚膜电阻</t>
+  </si>
+  <si>
+    <t>UNI-ROYAL(厚声)</t>
+  </si>
+  <si>
+    <t>C11660</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/datasheet/0402WGF1022TCE/12214.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type:Thick Film Resistor Resistance:10.2kΩ Tolerance:±1% Tolerance:±1% Power(Watts):62.5mW Voltage-Supply(Max):50V Temperature Coefficient:±100ppm/℃ Temperature Coefficient:±100ppm/℃ Operating Temperature:-55℃~+155℃ Operating Temperature:-55℃~+155℃ </t>
+  </si>
+  <si>
+    <t>gge49</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>RC0402FR-0727RL</t>
+  </si>
+  <si>
+    <t>64.4mm</t>
+  </si>
+  <si>
+    <t>-65.6mm</t>
+  </si>
+  <si>
+    <t>64.833mm</t>
+  </si>
+  <si>
+    <t>27Ω</t>
+  </si>
+  <si>
+    <t>厚膜电阻 27Ω ±1% 62.5mW</t>
+  </si>
+  <si>
+    <t>C138021</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/datasheet/RC0402FR-0727RL/149337.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type:Thick Film Resistor Resistance:27Ω Tolerance:±1% Tolerance:±1% Power(Watts):62.5mW Voltage-Supply(Max):50V Temperature Coefficient:±100ppm/℃ Temperature Coefficient:±100ppm/℃ Operating Temperature:-55℃~+155℃ Operating Temperature:-55℃~+155℃ </t>
+  </si>
+  <si>
+    <t>gge50</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>68.04mm</t>
+  </si>
+  <si>
+    <t>-61.883mm</t>
+  </si>
+  <si>
+    <t>67.607mm</t>
+  </si>
+  <si>
+    <t>gge51</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>70.307mm</t>
+  </si>
+  <si>
+    <t>-57.043mm</t>
+  </si>
+  <si>
+    <t>-56.611mm</t>
+  </si>
+  <si>
+    <t>gge29_0</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>RP2350B_C42415655</t>
+  </si>
+  <si>
+    <t>QFN-80_L10.0-W10.0-P0.40-TL-EP3.4</t>
+  </si>
+  <si>
+    <t>62.659mm</t>
+  </si>
+  <si>
+    <t>-55.321mm</t>
+  </si>
+  <si>
+    <t>67.566mm</t>
+  </si>
+  <si>
+    <t>-59.122mm</t>
+  </si>
+  <si>
+    <t>RP2350B</t>
+  </si>
+  <si>
+    <t>版本：A4 SC1510(13)-A4</t>
+  </si>
+  <si>
+    <t>Raspberry Pi(树莓派)</t>
+  </si>
+  <si>
+    <t>C42415655</t>
+  </si>
+  <si>
+    <t>QFN-80-EP(10x10)</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/datasheet/RP2350B/44413055.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of I/O:48 Features:Independent watchdog (IWDG)；Power-on reset (POR)；True random number generator (TRNG)；Watchdog reset；Built-in general-purpose timer；Hardware ECC check；External pin reset (NRST)；Integrated LDO </t>
+  </si>
+  <si>
+    <t>gge1</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>BNO055</t>
+  </si>
+  <si>
+    <t>LGA-28_L5.2-W3.8-P0.50-BL</t>
+  </si>
+  <si>
+    <t>48.7mm</t>
+  </si>
+  <si>
+    <t>-65.274mm</t>
+  </si>
+  <si>
+    <t>50.263mm</t>
+  </si>
+  <si>
+    <t>-63.024mm</t>
+  </si>
+  <si>
+    <t>LGA-28_L5.2-W3.8-H1.2-P0.50-BL</t>
+  </si>
+  <si>
+    <t>9轴绝对定向智能传感器</t>
+  </si>
+  <si>
+    <t>Bosch(博世)</t>
+  </si>
+  <si>
+    <t>C93216</t>
+  </si>
+  <si>
+    <t>LGA-28(3.8x5.2)</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/datasheet/BNO055/94411.html</t>
+  </si>
+  <si>
+    <t>Accelerometer Sensing Axis:X,Y,Z Acceleration Measurement Range (MAX):±16g Acceleration Measurement Range (MAX):±16g Gyroscope Sensing Axis:X,Y,Z Gyroscope Measurement Range (MAX):±2000dps Gyroscope Measurement Range (MAX):±2000dps Sensor Type:IMU (accele</t>
+  </si>
+  <si>
+    <t>gge2</t>
+  </si>
+  <si>
+    <t>-40℃~+85℃</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>BME680</t>
+  </si>
+  <si>
+    <t>LGA-8_L3.0-W3.0-P0.80-TR</t>
+  </si>
+  <si>
+    <t>52.7mm</t>
+  </si>
+  <si>
+    <t>-74.9mm</t>
+  </si>
+  <si>
+    <t>51.5mm</t>
+  </si>
+  <si>
+    <t>-73.5mm</t>
+  </si>
+  <si>
+    <t>LGA-8_L3.0-W3.0-H0.9-P0.80-TR</t>
+  </si>
+  <si>
+    <t>低功耗气体、压力、温度和湿度传感器</t>
+  </si>
+  <si>
+    <t>C125972</t>
+  </si>
+  <si>
+    <t>LGA-8</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/datasheet/BME680/137252.html</t>
+  </si>
+  <si>
+    <t>Pressure range:30Kpa~1.1bar Pressure range:30Kpa~1.1bar Voltage - Supply:1.71V~3.6V Voltage - Supply:1.71V~3.6V Standby Current:150nA Interface:SPI；I2C Module:- Absolute Accuracy:0.6hpa Relative Accuracy:0.12hpa Features:Standby mode；Integrated ADC and di</t>
+  </si>
+  <si>
+    <t>gge3</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
+    <t>INA226AIDGSR</t>
+  </si>
+  <si>
+    <t>MSOP-10_L3.0-W3.0-P0.50-LS5.0-BL</t>
+  </si>
+  <si>
+    <t>79.2mm</t>
+  </si>
+  <si>
+    <t>-72.4mm</t>
+  </si>
+  <si>
+    <t>80.2mm</t>
+  </si>
+  <si>
+    <t>-70.29mm</t>
+  </si>
+  <si>
+    <t>MSOP-10_L3.0-W3.0-H1.1-LS5.0-P0.50</t>
+  </si>
+  <si>
+    <t>高侧/低侧测量双向电流/功率监视器，具有I²C兼容接口</t>
+  </si>
+  <si>
+    <t>TI(德州仪器)</t>
+  </si>
+  <si>
+    <t>C49851</t>
+  </si>
+  <si>
+    <t>VSSOP-10</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/cn/lit/ds/symlink/ina226.pdf</t>
+  </si>
+  <si>
+    <t>Number of Channels:- Vcm - Common Mode Voltage:0V~36V Vcm - Common Mode Voltage:0V~36V Gain:- Bandwidth:- Ib - Input Bias Current:100pA Vos - Input Offset Voltage:2.5uV Operating Temperature:-40℃~+125℃ Operating Temperature:-40℃~+125℃ Differential Voltage</t>
+  </si>
+  <si>
+    <t>gge4</t>
+  </si>
+  <si>
+    <t>-40℃~+125℃</t>
+  </si>
+  <si>
+    <t>U5</t>
+  </si>
+  <si>
+    <t>LIS3MDLTR</t>
+  </si>
+  <si>
+    <t>LGA-12_L2.0-W2.0-P0.50-BL</t>
+  </si>
+  <si>
+    <t>65.4mm</t>
   </si>
   <si>
     <t>-42mm</t>
   </si>
   <si>
-    <t>-44.5mm</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>AMASS(艾迈斯)板载立式 航模锂电池控制器连接器插头 PCB板立式 公头XT30UPB-M.G.Y</t>
-  </si>
-  <si>
-    <t>AMASS(艾迈斯)</t>
-  </si>
-  <si>
-    <t>C428721</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/datasheet/XT30UPB-M/423831.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rated current:15A Rated voltage: colour:Yellow Connector type:Model aircraft plug contact resistance: interface form:Male insulating material: metal material:Gold plating </t>
-  </si>
-  <si>
-    <t>gge10</t>
-  </si>
-  <si>
-    <t>15A</t>
-  </si>
-  <si>
-    <t>Yellow</t>
-  </si>
-  <si>
-    <t>Model aircraft plug</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>Gold plating</t>
-  </si>
-  <si>
-    <t>CN2</t>
-  </si>
-  <si>
-    <t>BM04B-SRSS-TB(LF)(SN)</t>
-  </si>
-  <si>
-    <t>CONN-SMD_BM04B-SRSS-TB</t>
-  </si>
-  <si>
-    <t>72.9mm</t>
-  </si>
-  <si>
-    <t>-70.6mm</t>
-  </si>
-  <si>
-    <t>74.4mm</t>
-  </si>
-  <si>
-    <t>-69.337mm</t>
-  </si>
-  <si>
-    <t>CONN-SMD_4P-L6.0-W2.9-H4.3-P1.0</t>
-  </si>
-  <si>
-    <t>1x4P 间距:1mm 立贴 系列:SR</t>
-  </si>
-  <si>
-    <t>JST</t>
-  </si>
-  <si>
-    <t>C160390</t>
-  </si>
-  <si>
-    <t>SMD,P=1mm</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/datasheet/BM04B-SRSS-TB(LF)(SN)/171770.html</t>
-  </si>
-  <si>
-    <t>Pins Structure:1x4P Pitch:1mm Mounting Type:Surface Mount,Vertical Reference Series:SR Number of Pins:4P Number of Rows:1 Number of PINs Per Row:4 Row Spacing:- Current Rating:1A Contact Material:Copper alloy Contact Plating:Tin Operating Temperature:-25℃</t>
-  </si>
-  <si>
-    <t>gge15</t>
-  </si>
-  <si>
-    <t>Auxiliary Solder Pin</t>
-  </si>
-  <si>
-    <t>-25℃~+85℃</t>
-  </si>
-  <si>
-    <t>1x4P</t>
-  </si>
-  <si>
-    <t>1mm</t>
-  </si>
-  <si>
-    <t>Surface Mount,Vertical</t>
-  </si>
-  <si>
-    <t>SR</t>
-  </si>
-  <si>
-    <t>4P</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1A</t>
-  </si>
-  <si>
-    <t>Copper alloy</t>
-  </si>
-  <si>
-    <t>Tin</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>UL94V-0</t>
-  </si>
-  <si>
-    <t>3.6mm</t>
-  </si>
-  <si>
-    <t>D2</t>
-  </si>
-  <si>
-    <t>SS14_C112424</t>
-  </si>
-  <si>
-    <t>SMA_L4.4-W2.6-LS5.0-RD</t>
-  </si>
-  <si>
-    <t>49.396mm</t>
-  </si>
-  <si>
-    <t>-47.089mm</t>
-  </si>
-  <si>
-    <t>47.204mm</t>
-  </si>
-  <si>
-    <t>SS14</t>
-  </si>
-  <si>
-    <t>电压:40V 电流:1A</t>
-  </si>
-  <si>
-    <t>晶导微电子</t>
-  </si>
-  <si>
-    <t>C112424</t>
-  </si>
-  <si>
-    <t>SMA(DO-214AC)</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/datasheet/SS14/113656.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voltage - Forward(Vf@If):550mV@1A Voltage - DC Reverse(Vr):40V Current - Rectified:1A Reverse Leakage Current (Ir):300uA@40V Operating Junction Temperature Range:-55℃~+125℃ Operating Junction Temperature Range:-55℃~+125℃ Non-Repetitive Peak Forward Surge </t>
-  </si>
-  <si>
-    <t>gge27</t>
-  </si>
-  <si>
-    <t>H1</t>
-  </si>
-  <si>
-    <t>2011-1X14G00SB</t>
-  </si>
-  <si>
-    <t>HDR-TH_14P-P2.54-V-M_4</t>
-  </si>
-  <si>
-    <t>60.311mm</t>
-  </si>
-  <si>
-    <t>-33.472mm</t>
-  </si>
-  <si>
-    <t>43.801mm</t>
-  </si>
-  <si>
-    <t>1x14P 间距:2.54mm 方针 直插</t>
-  </si>
-  <si>
-    <t>WingTAT(格林柏)</t>
-  </si>
-  <si>
-    <t>C49569637</t>
-  </si>
-  <si>
-    <t>插件,P=2.54mm</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/datasheet/2011-1X14G00SB/52123945.html</t>
-  </si>
-  <si>
-    <t>Pin Structure:1x14P Pitch:2.54mm Circluar Pins/Square Pins:Pin Header Mounting Type:Through Hole Number of Rows:1 Number of Pins:14P Current Rating:3A Voltage Rating (Max):600V Length of Mating Pin:6mm Insulation Height:2.5mm Length of End Connection Pin:</t>
-  </si>
-  <si>
-    <t>gge16</t>
-  </si>
-  <si>
-    <t>-40℃~+105℃</t>
-  </si>
-  <si>
-    <t>2.54mm</t>
-  </si>
-  <si>
-    <t>Through Hole</t>
-  </si>
-  <si>
-    <t>14P</t>
-  </si>
-  <si>
-    <t>3A</t>
-  </si>
-  <si>
-    <t>Brass</t>
-  </si>
-  <si>
-    <t>Gold</t>
-  </si>
-  <si>
-    <t>2.5mm</t>
-  </si>
-  <si>
-    <t>6mm</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
-    <t>AOTA-B201610S3R3-101-T</t>
-  </si>
-  <si>
-    <t>IND-SMD_L2.0-W1.6_AOTA-B201610S3R3-101-T</t>
-  </si>
-  <si>
-    <t>50.875mm</t>
-  </si>
-  <si>
-    <t>-54.434mm</t>
-  </si>
-  <si>
-    <t>-54.426mm</t>
-  </si>
-  <si>
-    <t>-55.442mm</t>
-  </si>
-  <si>
-    <t>3.3uH</t>
-  </si>
-  <si>
-    <t>3.3uH 2.4A</t>
-  </si>
-  <si>
-    <t>ABRACON</t>
-  </si>
-  <si>
-    <t>C42411119</t>
-  </si>
-  <si>
-    <t>0806</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/datasheet/AOTA-B201610S3R3-101-T/44392932.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inductance:3.3uH Current Rating:2.1A Current - Saturation(Isat):2.4A DC Resistance(DCR):115mΩ Type:Molded Inductor </t>
-  </si>
-  <si>
-    <t>gge21</t>
-  </si>
-  <si>
-    <t>2.1A</t>
-  </si>
-  <si>
-    <t>R1</t>
-  </si>
-  <si>
-    <t>RC0402FR-071KL</t>
-  </si>
-  <si>
-    <t>R0402</t>
-  </si>
-  <si>
-    <t>48.178mm</t>
-  </si>
-  <si>
-    <t>-51.811mm</t>
-  </si>
-  <si>
-    <t>-52.244mm</t>
-  </si>
-  <si>
-    <t>1kΩ</t>
-  </si>
-  <si>
-    <t>R0402_L1.0-W0.5-H0.4</t>
-  </si>
-  <si>
-    <t>厚膜电阻 1kΩ ±1% 62.5mW</t>
-  </si>
-  <si>
-    <t>C106235</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/datasheet/RC0402FR-071KL/107450.html</t>
-  </si>
-  <si>
-    <t>±1%</t>
-  </si>
-  <si>
-    <t>±100ppm/℃</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type:Thick Film Resistor Resistance:1kΩ Tolerance:±1% Tolerance:±1% Power(Watts):62.5mW Voltage-Supply(Max):50V Temperature Coefficient:±100ppm/℃ Temperature Coefficient:±100ppm/℃ Operating Temperature:-55℃~+155℃ Operating Temperature:-55℃~+155℃ </t>
-  </si>
-  <si>
-    <t>gge20</t>
-  </si>
-  <si>
-    <t>-55℃~+155℃</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>RC0402FR-0733RL</t>
-  </si>
-  <si>
-    <t>56.36mm</t>
-  </si>
-  <si>
-    <t>-73.599mm</t>
-  </si>
-  <si>
-    <t>55.927mm</t>
-  </si>
-  <si>
-    <t>33Ω</t>
-  </si>
-  <si>
-    <t>厚膜电阻 33Ω ±1% 62.5mW</t>
-  </si>
-  <si>
-    <t>C138002</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/datasheet/RC0402FR-0733RL/149318.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type:Thick Film Resistor Resistance:33Ω Tolerance:±1% Tolerance:±1% Power(Watts):62.5mW Voltage-Supply(Max):50V Temperature Coefficient:±100ppm/℃ Temperature Coefficient:±100ppm/℃ Operating Temperature:-55℃~+155℃ Operating Temperature:-55℃~+155℃ </t>
-  </si>
-  <si>
-    <t>gge25</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>FRC0402F1002TS</t>
-  </si>
-  <si>
-    <t>47.7mm</t>
-  </si>
-  <si>
-    <t>-75.8mm</t>
-  </si>
-  <si>
-    <t>48.133mm</t>
-  </si>
-  <si>
-    <t>10kΩ</t>
-  </si>
-  <si>
-    <t>10kΩ ±1% 62.5mW 厚膜电阻</t>
-  </si>
-  <si>
-    <t>FOJAN(富捷)</t>
-  </si>
-  <si>
-    <t>C2906861</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/datasheet/FRC0402F1002TS/3180374.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type:Thick Film Resistor Resistance:10kΩ Tolerance:±1% Tolerance:±1% Power(Watts):62.5mW Voltage-Supply(Max):50V Temperature Coefficient:±100ppm/℃ Temperature Coefficient:±100ppm/℃ Operating Temperature:-55℃~+155℃ Operating Temperature:-55℃~+155℃ </t>
-  </si>
-  <si>
-    <t>gge28</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>63.2mm</t>
-  </si>
-  <si>
-    <t>-70.3mm</t>
-  </si>
-  <si>
-    <t>-70.733mm</t>
-  </si>
-  <si>
-    <t>gge29</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>RC0402FR-0756KL</t>
-  </si>
-  <si>
-    <t>69.1mm</t>
-  </si>
-  <si>
-    <t>-64.3mm</t>
-  </si>
-  <si>
-    <t>69.533mm</t>
-  </si>
-  <si>
-    <t>56kΩ</t>
-  </si>
-  <si>
-    <t>厚膜电阻 56kΩ ±1% 62.5mW</t>
-  </si>
-  <si>
-    <t>C114756</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/datasheet/RC0402FR-0756KL/116000.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type:Thick Film Resistor Resistance:56kΩ Tolerance:±1% Tolerance:±1% Power(Watts):62.5mW Voltage-Supply(Max):50V Temperature Coefficient:±100ppm/℃ Temperature Coefficient:±100ppm/℃ Operating Temperature:-55℃~+155℃ Operating Temperature:-55℃~+155℃ </t>
-  </si>
-  <si>
-    <t>gge48</t>
-  </si>
-  <si>
-    <t>R6</t>
-  </si>
-  <si>
-    <t>0402WGF1022TCE</t>
-  </si>
-  <si>
-    <t>48.388mm</t>
-  </si>
-  <si>
-    <t>-59.934mm</t>
-  </si>
-  <si>
-    <t>48.821mm</t>
-  </si>
-  <si>
-    <t>10.2kΩ</t>
-  </si>
-  <si>
-    <t>10.2kΩ ±1% 62.5mW 厚膜电阻</t>
-  </si>
-  <si>
-    <t>UNI-ROYAL(厚声)</t>
-  </si>
-  <si>
-    <t>C11660</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/datasheet/0402WGF1022TCE/12214.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type:Thick Film Resistor Resistance:10.2kΩ Tolerance:±1% Tolerance:±1% Power(Watts):62.5mW Voltage-Supply(Max):50V Temperature Coefficient:±100ppm/℃ Temperature Coefficient:±100ppm/℃ Operating Temperature:-55℃~+155℃ Operating Temperature:-55℃~+155℃ </t>
-  </si>
-  <si>
-    <t>gge49</t>
-  </si>
-  <si>
-    <t>R7</t>
-  </si>
-  <si>
-    <t>RC0402FR-0727RL</t>
-  </si>
-  <si>
-    <t>64.4mm</t>
-  </si>
-  <si>
-    <t>-65.6mm</t>
-  </si>
-  <si>
-    <t>64.833mm</t>
-  </si>
-  <si>
-    <t>27Ω</t>
-  </si>
-  <si>
-    <t>厚膜电阻 27Ω ±1% 62.5mW</t>
-  </si>
-  <si>
-    <t>C138021</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/datasheet/RC0402FR-0727RL/149337.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type:Thick Film Resistor Resistance:27Ω Tolerance:±1% Tolerance:±1% Power(Watts):62.5mW Voltage-Supply(Max):50V Temperature Coefficient:±100ppm/℃ Temperature Coefficient:±100ppm/℃ Operating Temperature:-55℃~+155℃ Operating Temperature:-55℃~+155℃ </t>
-  </si>
-  <si>
-    <t>gge50</t>
-  </si>
-  <si>
-    <t>R8</t>
-  </si>
-  <si>
-    <t>68.04mm</t>
-  </si>
-  <si>
-    <t>-61.883mm</t>
-  </si>
-  <si>
-    <t>67.607mm</t>
-  </si>
-  <si>
-    <t>gge51</t>
-  </si>
-  <si>
-    <t>R9</t>
-  </si>
-  <si>
-    <t>70.407mm</t>
-  </si>
-  <si>
-    <t>-54.543mm</t>
-  </si>
-  <si>
-    <t>-54.111mm</t>
-  </si>
-  <si>
-    <t>gge29_0</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>RP2350B_C42415655</t>
-  </si>
-  <si>
-    <t>QFN-80_L10.0-W10.0-P0.40-TL-EP3.4</t>
-  </si>
-  <si>
-    <t>62.659mm</t>
-  </si>
-  <si>
-    <t>-55.321mm</t>
-  </si>
-  <si>
-    <t>67.566mm</t>
-  </si>
-  <si>
-    <t>-59.122mm</t>
-  </si>
-  <si>
-    <t>RP2350B</t>
-  </si>
-  <si>
-    <t>版本：A4 SC1510(13)-A4</t>
-  </si>
-  <si>
-    <t>Raspberry Pi(树莓派)</t>
-  </si>
-  <si>
-    <t>C42415655</t>
-  </si>
-  <si>
-    <t>QFN-80-EP(10x10)</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/datasheet/RP2350B/44413055.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of I/O:48 Features:Independent watchdog (IWDG)；Power-on reset (POR)；True random number generator (TRNG)；Watchdog reset；Built-in general-purpose timer；Hardware ECC check；External pin reset (NRST)；Integrated LDO </t>
-  </si>
-  <si>
-    <t>gge1</t>
-  </si>
-  <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t>BNO055</t>
-  </si>
-  <si>
-    <t>LGA-28_L5.2-W3.8-P0.50-BL</t>
-  </si>
-  <si>
-    <t>48.7mm</t>
-  </si>
-  <si>
-    <t>-65.274mm</t>
-  </si>
-  <si>
-    <t>50.263mm</t>
-  </si>
-  <si>
-    <t>-63.024mm</t>
-  </si>
-  <si>
-    <t>LGA-28_L5.2-W3.8-H1.2-P0.50-BL</t>
-  </si>
-  <si>
-    <t>9轴绝对定向智能传感器</t>
-  </si>
-  <si>
-    <t>Bosch(博世)</t>
-  </si>
-  <si>
-    <t>C93216</t>
-  </si>
-  <si>
-    <t>LGA-28(3.8x5.2)</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/datasheet/BNO055/94411.html</t>
-  </si>
-  <si>
-    <t>Accelerometer Sensing Axis:X,Y,Z Acceleration Measurement Range (MAX):±16g Acceleration Measurement Range (MAX):±16g Gyroscope Sensing Axis:X,Y,Z Gyroscope Measurement Range (MAX):±2000dps Gyroscope Measurement Range (MAX):±2000dps Sensor Type:IMU (accele</t>
-  </si>
-  <si>
-    <t>gge2</t>
-  </si>
-  <si>
-    <t>-40℃~+85℃</t>
-  </si>
-  <si>
-    <t>U3</t>
-  </si>
-  <si>
-    <t>BME680</t>
-  </si>
-  <si>
-    <t>LGA-8_L3.0-W3.0-P0.80-TR</t>
-  </si>
-  <si>
-    <t>52.7mm</t>
-  </si>
-  <si>
-    <t>-74.9mm</t>
-  </si>
-  <si>
-    <t>51.5mm</t>
-  </si>
-  <si>
-    <t>-73.5mm</t>
-  </si>
-  <si>
-    <t>LGA-8_L3.0-W3.0-H0.9-P0.80-TR</t>
-  </si>
-  <si>
-    <t>低功耗气体、压力、温度和湿度传感器</t>
-  </si>
-  <si>
-    <t>C125972</t>
-  </si>
-  <si>
-    <t>LGA-8</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/datasheet/BME680/137252.html</t>
-  </si>
-  <si>
-    <t>Pressure range:30Kpa~1.1bar Pressure range:30Kpa~1.1bar Voltage - Supply:1.71V~3.6V Voltage - Supply:1.71V~3.6V Standby Current:150nA Interface:SPI；I2C Module:- Absolute Accuracy:0.6hpa Relative Accuracy:0.12hpa Features:Standby mode；Integrated ADC and di</t>
-  </si>
-  <si>
-    <t>gge3</t>
-  </si>
-  <si>
-    <t>U4</t>
-  </si>
-  <si>
-    <t>INA226AIDGSR</t>
-  </si>
-  <si>
-    <t>MSOP-10_L3.0-W3.0-P0.50-LS5.0-BL</t>
-  </si>
-  <si>
-    <t>79.2mm</t>
-  </si>
-  <si>
-    <t>-72.4mm</t>
-  </si>
-  <si>
-    <t>80.2mm</t>
-  </si>
-  <si>
-    <t>-70.29mm</t>
-  </si>
-  <si>
-    <t>MSOP-10_L3.0-W3.0-H1.1-LS5.0-P0.50</t>
-  </si>
-  <si>
-    <t>高侧/低侧测量双向电流/功率监视器，具有I²C兼容接口</t>
-  </si>
-  <si>
-    <t>TI(德州仪器)</t>
-  </si>
-  <si>
-    <t>C49851</t>
-  </si>
-  <si>
-    <t>VSSOP-10</t>
-  </si>
-  <si>
-    <t>https://www.ti.com/cn/lit/ds/symlink/ina226.pdf</t>
-  </si>
-  <si>
-    <t>Number of Channels:- Vcm - Common Mode Voltage:0V~36V Vcm - Common Mode Voltage:0V~36V Gain:- Bandwidth:- Ib - Input Bias Current:100pA Vos - Input Offset Voltage:2.5uV Operating Temperature:-40℃~+125℃ Operating Temperature:-40℃~+125℃ Differential Voltage</t>
-  </si>
-  <si>
-    <t>gge4</t>
-  </si>
-  <si>
-    <t>-40℃~+125℃</t>
-  </si>
-  <si>
-    <t>U5</t>
-  </si>
-  <si>
-    <t>LIS3MDLTR</t>
-  </si>
-  <si>
-    <t>LGA-12_L2.0-W2.0-P0.50-BL</t>
-  </si>
-  <si>
-    <t>64.6mm</t>
-  </si>
-  <si>
-    <t>-41.8mm</t>
-  </si>
-  <si>
-    <t>65.475mm</t>
-  </si>
-  <si>
-    <t>-42.55mm</t>
+    <t>66.275mm</t>
+  </si>
+  <si>
+    <t>-42.75mm</t>
   </si>
   <si>
     <t>LGA-12_L2.0-W2.0-H1.0-P0.50</t>
@@ -1567,13 +1567,13 @@
     <t>SW-TH_3P-L8.8-W3.9-P2.50_SS12D00G3</t>
   </si>
   <si>
-    <t>72.106mm</t>
-  </si>
-  <si>
-    <t>-77.52mm</t>
-  </si>
-  <si>
-    <t>74.606mm</t>
+    <t>72.3mm</t>
+  </si>
+  <si>
+    <t>-77.3mm</t>
+  </si>
+  <si>
+    <t>74.8mm</t>
   </si>
   <si>
     <t>大型拨动开关</t>
@@ -1756,10 +1756,10 @@
     <t>C10</t>
   </si>
   <si>
-    <t>-64.5mm</t>
-  </si>
-  <si>
-    <t>59.42mm</t>
+    <t>59.132mm</t>
+  </si>
+  <si>
+    <t>59.552mm</t>
   </si>
   <si>
     <t>gge30_3</t>
@@ -1843,13 +1843,13 @@
     <t>C16</t>
   </si>
   <si>
-    <t>66.08mm</t>
-  </si>
-  <si>
-    <t>-73.658mm</t>
-  </si>
-  <si>
-    <t>-74.078mm</t>
+    <t>66.5mm</t>
+  </si>
+  <si>
+    <t>-73.7mm</t>
+  </si>
+  <si>
+    <t>-74.12mm</t>
   </si>
   <si>
     <t>gge30_9</t>
@@ -1873,13 +1873,10 @@
     <t>C18</t>
   </si>
   <si>
-    <t>59.765mm</t>
-  </si>
-  <si>
-    <t>-47.042mm</t>
-  </si>
-  <si>
-    <t>60.185mm</t>
+    <t>-46.6mm</t>
+  </si>
+  <si>
+    <t>59.62mm</t>
   </si>
   <si>
     <t>gge30_11</t>
@@ -1903,13 +1900,13 @@
     <t>C20</t>
   </si>
   <si>
-    <t>67.588mm</t>
-  </si>
-  <si>
-    <t>-47.852mm</t>
-  </si>
-  <si>
-    <t>67.168mm</t>
+    <t>70.388mm</t>
+  </si>
+  <si>
+    <t>-48.452mm</t>
+  </si>
+  <si>
+    <t>69.968mm</t>
   </si>
   <si>
     <t>gge30_13</t>
@@ -2204,6 +2201,39 @@
   </si>
   <si>
     <t>5.5A</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>FRC0402J512 TS</t>
+  </si>
+  <si>
+    <t>59.791mm</t>
+  </si>
+  <si>
+    <t>-75.355mm</t>
+  </si>
+  <si>
+    <t>59.359mm</t>
+  </si>
+  <si>
+    <t>5.1kΩ</t>
+  </si>
+  <si>
+    <t>5.1kΩ ±5% 62.5mW 厚膜电阻</t>
+  </si>
+  <si>
+    <t>C2906948</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/datasheet/FRC0402J512%2520TS/3180461.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type:Thick Film Resistor Resistance:5.1kΩ Tolerance:±5% Tolerance:±5% Power(Watts):62.5mW Voltage-Supply(Max):50V Temperature Coefficient:±100ppm/℃ Temperature Coefficient:±100ppm/℃ Operating Temperature:-55℃~+155℃ Operating Temperature:-55℃~+155℃ </t>
+  </si>
+  <si>
+    <t>gge59</t>
   </si>
 </sst>
 </file>
@@ -2580,7 +2610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR61"/>
+  <dimension ref="A1:BR62"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="70" width="20" customWidth="1"/>
@@ -11289,22 +11319,22 @@
         <v>72</v>
       </c>
       <c r="D42" t="s">
-        <v>102</v>
+        <v>581</v>
       </c>
       <c r="E42" t="s">
+        <v>329</v>
+      </c>
+      <c r="F42" t="s">
         <v>581</v>
       </c>
-      <c r="F42" t="s">
-        <v>102</v>
-      </c>
       <c r="G42" t="s">
-        <v>581</v>
+        <v>329</v>
       </c>
       <c r="H42" t="s">
         <v>582</v>
       </c>
       <c r="I42" t="s">
-        <v>581</v>
+        <v>329</v>
       </c>
       <c r="J42">
         <v>2</v>
@@ -12985,22 +13015,22 @@
         <v>72</v>
       </c>
       <c r="D50" t="s">
+        <v>595</v>
+      </c>
+      <c r="E50" t="s">
         <v>620</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
+        <v>595</v>
+      </c>
+      <c r="G50" t="s">
+        <v>620</v>
+      </c>
+      <c r="H50" t="s">
         <v>621</v>
       </c>
-      <c r="F50" t="s">
+      <c r="I50" t="s">
         <v>620</v>
-      </c>
-      <c r="G50" t="s">
-        <v>621</v>
-      </c>
-      <c r="H50" t="s">
-        <v>622</v>
-      </c>
-      <c r="I50" t="s">
-        <v>621</v>
       </c>
       <c r="J50">
         <v>2</v>
@@ -13066,7 +13096,7 @@
         <v>139</v>
       </c>
       <c r="AE50" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AF50" t="s">
         <v>93</v>
@@ -13188,7 +13218,7 @@
     </row>
     <row r="51" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B51" t="s">
         <v>129</v>
@@ -13197,22 +13227,22 @@
         <v>72</v>
       </c>
       <c r="D51" t="s">
+        <v>624</v>
+      </c>
+      <c r="E51" t="s">
         <v>625</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
+        <v>624</v>
+      </c>
+      <c r="G51" t="s">
+        <v>625</v>
+      </c>
+      <c r="H51" t="s">
+        <v>624</v>
+      </c>
+      <c r="I51" t="s">
         <v>626</v>
-      </c>
-      <c r="F51" t="s">
-        <v>625</v>
-      </c>
-      <c r="G51" t="s">
-        <v>626</v>
-      </c>
-      <c r="H51" t="s">
-        <v>625</v>
-      </c>
-      <c r="I51" t="s">
-        <v>627</v>
       </c>
       <c r="J51">
         <v>2</v>
@@ -13278,7 +13308,7 @@
         <v>139</v>
       </c>
       <c r="AE51" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AF51" t="s">
         <v>93</v>
@@ -13400,7 +13430,7 @@
     </row>
     <row r="52" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B52" t="s">
         <v>129</v>
@@ -13409,22 +13439,22 @@
         <v>72</v>
       </c>
       <c r="D52" t="s">
+        <v>629</v>
+      </c>
+      <c r="E52" t="s">
         <v>630</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
+        <v>629</v>
+      </c>
+      <c r="G52" t="s">
+        <v>630</v>
+      </c>
+      <c r="H52" t="s">
         <v>631</v>
       </c>
-      <c r="F52" t="s">
+      <c r="I52" t="s">
         <v>630</v>
-      </c>
-      <c r="G52" t="s">
-        <v>631</v>
-      </c>
-      <c r="H52" t="s">
-        <v>632</v>
-      </c>
-      <c r="I52" t="s">
-        <v>631</v>
       </c>
       <c r="J52">
         <v>2</v>
@@ -13490,7 +13520,7 @@
         <v>139</v>
       </c>
       <c r="AE52" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AF52" t="s">
         <v>93</v>
@@ -13612,7 +13642,7 @@
     </row>
     <row r="53" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B53" t="s">
         <v>129</v>
@@ -13621,22 +13651,22 @@
         <v>72</v>
       </c>
       <c r="D53" t="s">
+        <v>634</v>
+      </c>
+      <c r="E53" t="s">
         <v>635</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
+        <v>634</v>
+      </c>
+      <c r="G53" t="s">
+        <v>635</v>
+      </c>
+      <c r="H53" t="s">
+        <v>634</v>
+      </c>
+      <c r="I53" t="s">
         <v>636</v>
-      </c>
-      <c r="F53" t="s">
-        <v>635</v>
-      </c>
-      <c r="G53" t="s">
-        <v>636</v>
-      </c>
-      <c r="H53" t="s">
-        <v>635</v>
-      </c>
-      <c r="I53" t="s">
-        <v>637</v>
       </c>
       <c r="J53">
         <v>2</v>
@@ -13702,7 +13732,7 @@
         <v>139</v>
       </c>
       <c r="AE53" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AF53" t="s">
         <v>93</v>
@@ -13824,31 +13854,31 @@
     </row>
     <row r="54" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>638</v>
+      </c>
+      <c r="B54" t="s">
         <v>639</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>640</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>641</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>642</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
+        <v>641</v>
+      </c>
+      <c r="G54" t="s">
+        <v>642</v>
+      </c>
+      <c r="H54" t="s">
+        <v>641</v>
+      </c>
+      <c r="I54" t="s">
         <v>643</v>
-      </c>
-      <c r="F54" t="s">
-        <v>642</v>
-      </c>
-      <c r="G54" t="s">
-        <v>643</v>
-      </c>
-      <c r="H54" t="s">
-        <v>642</v>
-      </c>
-      <c r="I54" t="s">
-        <v>644</v>
       </c>
       <c r="J54">
         <v>3</v>
@@ -13863,25 +13893,25 @@
         <v>188</v>
       </c>
       <c r="N54" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="O54" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="P54" t="s">
+        <v>644</v>
+      </c>
+      <c r="Q54" t="s">
         <v>645</v>
       </c>
-      <c r="Q54" t="s">
+      <c r="R54" t="s">
         <v>646</v>
       </c>
-      <c r="R54" t="s">
+      <c r="S54" t="s">
         <v>647</v>
       </c>
-      <c r="S54" t="s">
-        <v>648</v>
-      </c>
       <c r="T54" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="U54" t="s">
         <v>253</v>
@@ -13890,7 +13920,7 @@
         <v>111</v>
       </c>
       <c r="W54" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="X54" t="s">
         <v>86</v>
@@ -13911,10 +13941,10 @@
         <v>93</v>
       </c>
       <c r="AD54" t="s">
+        <v>649</v>
+      </c>
+      <c r="AE54" t="s">
         <v>650</v>
-      </c>
-      <c r="AE54" t="s">
-        <v>651</v>
       </c>
       <c r="AF54" t="s">
         <v>93</v>
@@ -14036,7 +14066,7 @@
     </row>
     <row r="55" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B55" t="s">
         <v>283</v>
@@ -14045,22 +14075,22 @@
         <v>284</v>
       </c>
       <c r="D55" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E55" t="s">
         <v>323</v>
       </c>
       <c r="F55" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G55" t="s">
         <v>323</v>
       </c>
       <c r="H55" t="s">
+        <v>652</v>
+      </c>
+      <c r="I55" t="s">
         <v>653</v>
-      </c>
-      <c r="I55" t="s">
-        <v>654</v>
       </c>
       <c r="J55">
         <v>2</v>
@@ -14126,7 +14156,7 @@
         <v>295</v>
       </c>
       <c r="AE55" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="AF55" t="s">
         <v>93</v>
@@ -14248,31 +14278,31 @@
     </row>
     <row r="56" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>655</v>
+      </c>
+      <c r="B56" t="s">
         <v>656</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>657</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>658</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>659</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
+        <v>658</v>
+      </c>
+      <c r="G56" t="s">
+        <v>659</v>
+      </c>
+      <c r="H56" t="s">
         <v>660</v>
       </c>
-      <c r="F56" t="s">
-        <v>659</v>
-      </c>
-      <c r="G56" t="s">
-        <v>660</v>
-      </c>
-      <c r="H56" t="s">
+      <c r="I56" t="s">
         <v>661</v>
-      </c>
-      <c r="I56" t="s">
-        <v>662</v>
       </c>
       <c r="J56">
         <v>4</v>
@@ -14287,34 +14317,34 @@
         <v>77</v>
       </c>
       <c r="N56" t="s">
+        <v>656</v>
+      </c>
+      <c r="O56" t="s">
+        <v>656</v>
+      </c>
+      <c r="P56" t="s">
         <v>657</v>
       </c>
-      <c r="O56" t="s">
-        <v>657</v>
-      </c>
-      <c r="P56" t="s">
-        <v>658</v>
-      </c>
       <c r="Q56" t="s">
+        <v>662</v>
+      </c>
+      <c r="R56" t="s">
         <v>663</v>
       </c>
-      <c r="R56" t="s">
+      <c r="S56" t="s">
         <v>664</v>
       </c>
-      <c r="S56" t="s">
+      <c r="T56" t="s">
+        <v>656</v>
+      </c>
+      <c r="U56" t="s">
         <v>665</v>
-      </c>
-      <c r="T56" t="s">
-        <v>657</v>
-      </c>
-      <c r="U56" t="s">
-        <v>666</v>
       </c>
       <c r="V56" t="s">
         <v>84</v>
       </c>
       <c r="W56" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="X56" t="s">
         <v>86</v>
@@ -14329,37 +14359,37 @@
         <v>93</v>
       </c>
       <c r="AB56" t="s">
+        <v>667</v>
+      </c>
+      <c r="AC56" t="s">
+        <v>93</v>
+      </c>
+      <c r="AD56" t="s">
         <v>668</v>
       </c>
-      <c r="AC56" t="s">
-        <v>93</v>
-      </c>
-      <c r="AD56" t="s">
+      <c r="AE56" t="s">
         <v>669</v>
       </c>
-      <c r="AE56" t="s">
+      <c r="AF56" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG56" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH56" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI56" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ56" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK56" t="s">
+        <v>93</v>
+      </c>
+      <c r="AL56" t="s">
         <v>670</v>
-      </c>
-      <c r="AF56" t="s">
-        <v>93</v>
-      </c>
-      <c r="AG56" t="s">
-        <v>93</v>
-      </c>
-      <c r="AH56" t="s">
-        <v>93</v>
-      </c>
-      <c r="AI56" t="s">
-        <v>93</v>
-      </c>
-      <c r="AJ56" t="s">
-        <v>93</v>
-      </c>
-      <c r="AK56" t="s">
-        <v>93</v>
-      </c>
-      <c r="AL56" t="s">
-        <v>671</v>
       </c>
       <c r="AM56" t="s">
         <v>93</v>
@@ -14434,16 +14464,16 @@
         <v>93</v>
       </c>
       <c r="BK56" t="s">
+        <v>671</v>
+      </c>
+      <c r="BL56" t="s">
+        <v>671</v>
+      </c>
+      <c r="BM56" t="s">
+        <v>93</v>
+      </c>
+      <c r="BN56" t="s">
         <v>672</v>
-      </c>
-      <c r="BL56" t="s">
-        <v>672</v>
-      </c>
-      <c r="BM56" t="s">
-        <v>93</v>
-      </c>
-      <c r="BN56" t="s">
-        <v>673</v>
       </c>
       <c r="BO56" t="s">
         <v>93</v>
@@ -14460,7 +14490,7 @@
     </row>
     <row r="57" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B57" t="s">
         <v>129</v>
@@ -14469,22 +14499,22 @@
         <v>72</v>
       </c>
       <c r="D57" t="s">
+        <v>674</v>
+      </c>
+      <c r="E57" t="s">
         <v>675</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
+        <v>674</v>
+      </c>
+      <c r="G57" t="s">
+        <v>675</v>
+      </c>
+      <c r="H57" t="s">
         <v>676</v>
       </c>
-      <c r="F57" t="s">
+      <c r="I57" t="s">
         <v>675</v>
-      </c>
-      <c r="G57" t="s">
-        <v>676</v>
-      </c>
-      <c r="H57" t="s">
-        <v>677</v>
-      </c>
-      <c r="I57" t="s">
-        <v>676</v>
       </c>
       <c r="J57">
         <v>2</v>
@@ -14550,7 +14580,7 @@
         <v>139</v>
       </c>
       <c r="AE57" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AF57" t="s">
         <v>93</v>
@@ -14672,31 +14702,31 @@
     </row>
     <row r="58" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>678</v>
+      </c>
+      <c r="B58" t="s">
         <v>679</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>680</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>681</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>682</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
+        <v>681</v>
+      </c>
+      <c r="G58" t="s">
+        <v>682</v>
+      </c>
+      <c r="H58" t="s">
         <v>683</v>
       </c>
-      <c r="F58" t="s">
-        <v>682</v>
-      </c>
-      <c r="G58" t="s">
-        <v>683</v>
-      </c>
-      <c r="H58" t="s">
+      <c r="I58" t="s">
         <v>684</v>
-      </c>
-      <c r="I58" t="s">
-        <v>685</v>
       </c>
       <c r="J58">
         <v>8</v>
@@ -14711,34 +14741,34 @@
         <v>77</v>
       </c>
       <c r="N58" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="O58" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="P58" t="s">
+        <v>685</v>
+      </c>
+      <c r="Q58" t="s">
         <v>686</v>
       </c>
-      <c r="Q58" t="s">
+      <c r="R58" t="s">
         <v>687</v>
       </c>
-      <c r="R58" t="s">
+      <c r="S58" t="s">
         <v>688</v>
       </c>
-      <c r="S58" t="s">
+      <c r="T58" t="s">
+        <v>679</v>
+      </c>
+      <c r="U58" t="s">
         <v>689</v>
-      </c>
-      <c r="T58" t="s">
-        <v>680</v>
-      </c>
-      <c r="U58" t="s">
-        <v>690</v>
       </c>
       <c r="V58" t="s">
         <v>111</v>
       </c>
       <c r="W58" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="X58" t="s">
         <v>86</v>
@@ -14759,10 +14789,10 @@
         <v>93</v>
       </c>
       <c r="AD58" t="s">
+        <v>691</v>
+      </c>
+      <c r="AE58" t="s">
         <v>692</v>
-      </c>
-      <c r="AE58" t="s">
-        <v>693</v>
       </c>
       <c r="AF58" t="s">
         <v>93</v>
@@ -14884,7 +14914,7 @@
     </row>
     <row r="59" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B59" t="s">
         <v>129</v>
@@ -14893,22 +14923,22 @@
         <v>72</v>
       </c>
       <c r="D59" t="s">
+        <v>694</v>
+      </c>
+      <c r="E59" t="s">
         <v>695</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
+        <v>694</v>
+      </c>
+      <c r="G59" t="s">
+        <v>695</v>
+      </c>
+      <c r="H59" t="s">
         <v>696</v>
       </c>
-      <c r="F59" t="s">
+      <c r="I59" t="s">
         <v>695</v>
-      </c>
-      <c r="G59" t="s">
-        <v>696</v>
-      </c>
-      <c r="H59" t="s">
-        <v>697</v>
-      </c>
-      <c r="I59" t="s">
-        <v>696</v>
       </c>
       <c r="J59">
         <v>2</v>
@@ -14974,7 +15004,7 @@
         <v>139</v>
       </c>
       <c r="AE59" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="AF59" t="s">
         <v>93</v>
@@ -15096,31 +15126,31 @@
     </row>
     <row r="60" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>698</v>
+      </c>
+      <c r="B60" t="s">
         <v>699</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>700</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
         <v>701</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>702</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
+        <v>701</v>
+      </c>
+      <c r="G60" t="s">
+        <v>702</v>
+      </c>
+      <c r="H60" t="s">
         <v>703</v>
       </c>
-      <c r="F60" t="s">
-        <v>702</v>
-      </c>
-      <c r="G60" t="s">
-        <v>703</v>
-      </c>
-      <c r="H60" t="s">
+      <c r="I60" t="s">
         <v>704</v>
-      </c>
-      <c r="I60" t="s">
-        <v>705</v>
       </c>
       <c r="J60">
         <v>6</v>
@@ -15135,34 +15165,34 @@
         <v>77</v>
       </c>
       <c r="N60" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="O60" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="P60" t="s">
+        <v>705</v>
+      </c>
+      <c r="Q60" t="s">
         <v>706</v>
-      </c>
-      <c r="Q60" t="s">
-        <v>707</v>
       </c>
       <c r="R60" t="s">
         <v>424</v>
       </c>
       <c r="S60" t="s">
+        <v>707</v>
+      </c>
+      <c r="T60" t="s">
+        <v>699</v>
+      </c>
+      <c r="U60" t="s">
         <v>708</v>
-      </c>
-      <c r="T60" t="s">
-        <v>700</v>
-      </c>
-      <c r="U60" t="s">
-        <v>709</v>
       </c>
       <c r="V60" t="s">
         <v>111</v>
       </c>
       <c r="W60" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="X60" t="s">
         <v>86</v>
@@ -15183,156 +15213,156 @@
         <v>93</v>
       </c>
       <c r="AD60" t="s">
+        <v>710</v>
+      </c>
+      <c r="AE60" t="s">
         <v>711</v>
       </c>
-      <c r="AE60" t="s">
+      <c r="AF60" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG60" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH60" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI60" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ60" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK60" t="s">
+        <v>93</v>
+      </c>
+      <c r="AL60" t="s">
         <v>712</v>
       </c>
-      <c r="AF60" t="s">
-        <v>93</v>
-      </c>
-      <c r="AG60" t="s">
-        <v>93</v>
-      </c>
-      <c r="AH60" t="s">
-        <v>93</v>
-      </c>
-      <c r="AI60" t="s">
-        <v>93</v>
-      </c>
-      <c r="AJ60" t="s">
-        <v>93</v>
-      </c>
-      <c r="AK60" t="s">
-        <v>93</v>
-      </c>
-      <c r="AL60" t="s">
+      <c r="AM60" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN60" t="s">
+        <v>93</v>
+      </c>
+      <c r="AO60" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP60" t="s">
+        <v>93</v>
+      </c>
+      <c r="AQ60" t="s">
+        <v>93</v>
+      </c>
+      <c r="AR60" t="s">
+        <v>93</v>
+      </c>
+      <c r="AS60" t="s">
+        <v>93</v>
+      </c>
+      <c r="AT60" t="s">
+        <v>93</v>
+      </c>
+      <c r="AU60" t="s">
+        <v>93</v>
+      </c>
+      <c r="AV60" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW60" t="s">
+        <v>93</v>
+      </c>
+      <c r="AX60" t="s">
+        <v>93</v>
+      </c>
+      <c r="AY60" t="s">
+        <v>93</v>
+      </c>
+      <c r="AZ60" t="s">
+        <v>93</v>
+      </c>
+      <c r="BA60" t="s">
+        <v>93</v>
+      </c>
+      <c r="BB60" t="s">
+        <v>93</v>
+      </c>
+      <c r="BC60" t="s">
+        <v>93</v>
+      </c>
+      <c r="BD60" t="s">
+        <v>93</v>
+      </c>
+      <c r="BE60" t="s">
+        <v>93</v>
+      </c>
+      <c r="BF60" t="s">
+        <v>93</v>
+      </c>
+      <c r="BG60" t="s">
+        <v>93</v>
+      </c>
+      <c r="BH60" t="s">
+        <v>93</v>
+      </c>
+      <c r="BI60" t="s">
+        <v>93</v>
+      </c>
+      <c r="BJ60" t="s">
+        <v>93</v>
+      </c>
+      <c r="BK60" t="s">
+        <v>93</v>
+      </c>
+      <c r="BL60" t="s">
+        <v>93</v>
+      </c>
+      <c r="BM60" t="s">
+        <v>93</v>
+      </c>
+      <c r="BN60" t="s">
+        <v>93</v>
+      </c>
+      <c r="BO60" t="s">
+        <v>93</v>
+      </c>
+      <c r="BP60" t="s">
+        <v>93</v>
+      </c>
+      <c r="BQ60" t="s">
         <v>713</v>
       </c>
-      <c r="AM60" t="s">
-        <v>93</v>
-      </c>
-      <c r="AN60" t="s">
-        <v>93</v>
-      </c>
-      <c r="AO60" t="s">
-        <v>93</v>
-      </c>
-      <c r="AP60" t="s">
-        <v>93</v>
-      </c>
-      <c r="AQ60" t="s">
-        <v>93</v>
-      </c>
-      <c r="AR60" t="s">
-        <v>93</v>
-      </c>
-      <c r="AS60" t="s">
-        <v>93</v>
-      </c>
-      <c r="AT60" t="s">
-        <v>93</v>
-      </c>
-      <c r="AU60" t="s">
-        <v>93</v>
-      </c>
-      <c r="AV60" t="s">
-        <v>93</v>
-      </c>
-      <c r="AW60" t="s">
-        <v>93</v>
-      </c>
-      <c r="AX60" t="s">
-        <v>93</v>
-      </c>
-      <c r="AY60" t="s">
-        <v>93</v>
-      </c>
-      <c r="AZ60" t="s">
-        <v>93</v>
-      </c>
-      <c r="BA60" t="s">
-        <v>93</v>
-      </c>
-      <c r="BB60" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC60" t="s">
-        <v>93</v>
-      </c>
-      <c r="BD60" t="s">
-        <v>93</v>
-      </c>
-      <c r="BE60" t="s">
-        <v>93</v>
-      </c>
-      <c r="BF60" t="s">
-        <v>93</v>
-      </c>
-      <c r="BG60" t="s">
-        <v>93</v>
-      </c>
-      <c r="BH60" t="s">
-        <v>93</v>
-      </c>
-      <c r="BI60" t="s">
-        <v>93</v>
-      </c>
-      <c r="BJ60" t="s">
-        <v>93</v>
-      </c>
-      <c r="BK60" t="s">
-        <v>93</v>
-      </c>
-      <c r="BL60" t="s">
-        <v>93</v>
-      </c>
-      <c r="BM60" t="s">
-        <v>93</v>
-      </c>
-      <c r="BN60" t="s">
-        <v>93</v>
-      </c>
-      <c r="BO60" t="s">
-        <v>93</v>
-      </c>
-      <c r="BP60" t="s">
-        <v>93</v>
-      </c>
-      <c r="BQ60" t="s">
+      <c r="BR60" t="s">
         <v>714</v>
-      </c>
-      <c r="BR60" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="61" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>715</v>
+      </c>
+      <c r="B61" t="s">
         <v>716</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>717</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>718</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>719</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
+        <v>718</v>
+      </c>
+      <c r="G61" t="s">
+        <v>719</v>
+      </c>
+      <c r="H61" t="s">
         <v>720</v>
       </c>
-      <c r="F61" t="s">
+      <c r="I61" t="s">
         <v>719</v>
-      </c>
-      <c r="G61" t="s">
-        <v>720</v>
-      </c>
-      <c r="H61" t="s">
-        <v>721</v>
-      </c>
-      <c r="I61" t="s">
-        <v>720</v>
       </c>
       <c r="J61">
         <v>2</v>
@@ -15347,34 +15377,34 @@
         <v>77</v>
       </c>
       <c r="N61" t="s">
+        <v>721</v>
+      </c>
+      <c r="O61" t="s">
+        <v>721</v>
+      </c>
+      <c r="P61" t="s">
+        <v>717</v>
+      </c>
+      <c r="Q61" t="s">
         <v>722</v>
       </c>
-      <c r="O61" t="s">
-        <v>722</v>
-      </c>
-      <c r="P61" t="s">
-        <v>718</v>
-      </c>
-      <c r="Q61" t="s">
+      <c r="R61" t="s">
         <v>723</v>
       </c>
-      <c r="R61" t="s">
+      <c r="S61" t="s">
         <v>724</v>
       </c>
-      <c r="S61" t="s">
+      <c r="T61" t="s">
+        <v>716</v>
+      </c>
+      <c r="U61" t="s">
         <v>725</v>
-      </c>
-      <c r="T61" t="s">
-        <v>717</v>
-      </c>
-      <c r="U61" t="s">
-        <v>726</v>
       </c>
       <c r="V61" t="s">
         <v>111</v>
       </c>
       <c r="W61" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="X61" t="s">
         <v>86</v>
@@ -15383,7 +15413,7 @@
         <v>87</v>
       </c>
       <c r="Z61" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AA61" t="s">
         <v>153</v>
@@ -15395,126 +15425,338 @@
         <v>93</v>
       </c>
       <c r="AD61" t="s">
+        <v>727</v>
+      </c>
+      <c r="AE61" t="s">
         <v>728</v>
       </c>
-      <c r="AE61" t="s">
+      <c r="AF61" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG61" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH61" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI61" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ61" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK61" t="s">
+        <v>93</v>
+      </c>
+      <c r="AL61" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM61" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN61" t="s">
+        <v>93</v>
+      </c>
+      <c r="AO61" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP61" t="s">
+        <v>93</v>
+      </c>
+      <c r="AQ61" t="s">
+        <v>93</v>
+      </c>
+      <c r="AR61" t="s">
+        <v>93</v>
+      </c>
+      <c r="AS61" t="s">
+        <v>93</v>
+      </c>
+      <c r="AT61" t="s">
+        <v>93</v>
+      </c>
+      <c r="AU61" t="s">
+        <v>93</v>
+      </c>
+      <c r="AV61" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW61" t="s">
+        <v>93</v>
+      </c>
+      <c r="AX61" t="s">
+        <v>93</v>
+      </c>
+      <c r="AY61" t="s">
+        <v>93</v>
+      </c>
+      <c r="AZ61" t="s">
+        <v>93</v>
+      </c>
+      <c r="BA61" t="s">
+        <v>93</v>
+      </c>
+      <c r="BB61" t="s">
+        <v>93</v>
+      </c>
+      <c r="BC61" t="s">
         <v>729</v>
       </c>
-      <c r="AF61" t="s">
-        <v>93</v>
-      </c>
-      <c r="AG61" t="s">
-        <v>93</v>
-      </c>
-      <c r="AH61" t="s">
-        <v>93</v>
-      </c>
-      <c r="AI61" t="s">
-        <v>93</v>
-      </c>
-      <c r="AJ61" t="s">
-        <v>93</v>
-      </c>
-      <c r="AK61" t="s">
-        <v>93</v>
-      </c>
-      <c r="AL61" t="s">
-        <v>93</v>
-      </c>
-      <c r="AM61" t="s">
-        <v>93</v>
-      </c>
-      <c r="AN61" t="s">
-        <v>93</v>
-      </c>
-      <c r="AO61" t="s">
-        <v>93</v>
-      </c>
-      <c r="AP61" t="s">
-        <v>93</v>
-      </c>
-      <c r="AQ61" t="s">
-        <v>93</v>
-      </c>
-      <c r="AR61" t="s">
-        <v>93</v>
-      </c>
-      <c r="AS61" t="s">
-        <v>93</v>
-      </c>
-      <c r="AT61" t="s">
-        <v>93</v>
-      </c>
-      <c r="AU61" t="s">
-        <v>93</v>
-      </c>
-      <c r="AV61" t="s">
-        <v>93</v>
-      </c>
-      <c r="AW61" t="s">
-        <v>93</v>
-      </c>
-      <c r="AX61" t="s">
-        <v>93</v>
-      </c>
-      <c r="AY61" t="s">
-        <v>93</v>
-      </c>
-      <c r="AZ61" t="s">
-        <v>93</v>
-      </c>
-      <c r="BA61" t="s">
-        <v>93</v>
-      </c>
-      <c r="BB61" t="s">
-        <v>93</v>
-      </c>
-      <c r="BC61" t="s">
+      <c r="BD61" t="s">
+        <v>93</v>
+      </c>
+      <c r="BE61" t="s">
+        <v>93</v>
+      </c>
+      <c r="BF61" t="s">
+        <v>93</v>
+      </c>
+      <c r="BG61" t="s">
+        <v>93</v>
+      </c>
+      <c r="BH61" t="s">
+        <v>93</v>
+      </c>
+      <c r="BI61" t="s">
+        <v>93</v>
+      </c>
+      <c r="BJ61" t="s">
+        <v>93</v>
+      </c>
+      <c r="BK61" t="s">
+        <v>93</v>
+      </c>
+      <c r="BL61" t="s">
+        <v>93</v>
+      </c>
+      <c r="BM61" t="s">
+        <v>93</v>
+      </c>
+      <c r="BN61" t="s">
+        <v>93</v>
+      </c>
+      <c r="BO61" t="s">
+        <v>93</v>
+      </c>
+      <c r="BP61" t="s">
+        <v>93</v>
+      </c>
+      <c r="BQ61" t="s">
+        <v>93</v>
+      </c>
+      <c r="BR61" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="62" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>730</v>
       </c>
-      <c r="BD61" t="s">
-        <v>93</v>
-      </c>
-      <c r="BE61" t="s">
-        <v>93</v>
-      </c>
-      <c r="BF61" t="s">
-        <v>93</v>
-      </c>
-      <c r="BG61" t="s">
-        <v>93</v>
-      </c>
-      <c r="BH61" t="s">
-        <v>93</v>
-      </c>
-      <c r="BI61" t="s">
-        <v>93</v>
-      </c>
-      <c r="BJ61" t="s">
-        <v>93</v>
-      </c>
-      <c r="BK61" t="s">
-        <v>93</v>
-      </c>
-      <c r="BL61" t="s">
-        <v>93</v>
-      </c>
-      <c r="BM61" t="s">
-        <v>93</v>
-      </c>
-      <c r="BN61" t="s">
-        <v>93</v>
-      </c>
-      <c r="BO61" t="s">
-        <v>93</v>
-      </c>
-      <c r="BP61" t="s">
-        <v>93</v>
-      </c>
-      <c r="BQ61" t="s">
-        <v>93</v>
-      </c>
-      <c r="BR61" t="s">
+      <c r="B62" t="s">
+        <v>731</v>
+      </c>
+      <c r="C62" t="s">
+        <v>284</v>
+      </c>
+      <c r="D62" t="s">
+        <v>732</v>
+      </c>
+      <c r="E62" t="s">
+        <v>733</v>
+      </c>
+      <c r="F62" t="s">
+        <v>732</v>
+      </c>
+      <c r="G62" t="s">
+        <v>733</v>
+      </c>
+      <c r="H62" t="s">
+        <v>734</v>
+      </c>
+      <c r="I62" t="s">
+        <v>733</v>
+      </c>
+      <c r="J62">
+        <v>2</v>
+      </c>
+      <c r="K62" t="s">
+        <v>76</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62" t="s">
+        <v>77</v>
+      </c>
+      <c r="N62" t="s">
+        <v>735</v>
+      </c>
+      <c r="O62" t="s">
+        <v>735</v>
+      </c>
+      <c r="P62" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>736</v>
+      </c>
+      <c r="R62" t="s">
+        <v>316</v>
+      </c>
+      <c r="S62" t="s">
+        <v>737</v>
+      </c>
+      <c r="T62" t="s">
+        <v>731</v>
+      </c>
+      <c r="U62" t="s">
+        <v>83</v>
+      </c>
+      <c r="V62" t="s">
+        <v>111</v>
+      </c>
+      <c r="W62" t="s">
+        <v>738</v>
+      </c>
+      <c r="X62" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>735</v>
+      </c>
+      <c r="AA62" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB62" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC62" t="s">
+        <v>294</v>
+      </c>
+      <c r="AD62" t="s">
+        <v>739</v>
+      </c>
+      <c r="AE62" t="s">
+        <v>740</v>
+      </c>
+      <c r="AF62" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG62" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH62" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI62" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ62" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK62" t="s">
+        <v>93</v>
+      </c>
+      <c r="AL62" t="s">
+        <v>297</v>
+      </c>
+      <c r="AM62" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN62" t="s">
+        <v>93</v>
+      </c>
+      <c r="AO62" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP62" t="s">
+        <v>93</v>
+      </c>
+      <c r="AQ62" t="s">
+        <v>93</v>
+      </c>
+      <c r="AR62" t="s">
+        <v>93</v>
+      </c>
+      <c r="AS62" t="s">
+        <v>93</v>
+      </c>
+      <c r="AT62" t="s">
+        <v>93</v>
+      </c>
+      <c r="AU62" t="s">
+        <v>93</v>
+      </c>
+      <c r="AV62" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW62" t="s">
+        <v>93</v>
+      </c>
+      <c r="AX62" t="s">
+        <v>93</v>
+      </c>
+      <c r="AY62" t="s">
+        <v>93</v>
+      </c>
+      <c r="AZ62" t="s">
+        <v>93</v>
+      </c>
+      <c r="BA62" t="s">
+        <v>93</v>
+      </c>
+      <c r="BB62" t="s">
+        <v>93</v>
+      </c>
+      <c r="BC62" t="s">
+        <v>93</v>
+      </c>
+      <c r="BD62" t="s">
+        <v>93</v>
+      </c>
+      <c r="BE62" t="s">
+        <v>93</v>
+      </c>
+      <c r="BF62" t="s">
+        <v>93</v>
+      </c>
+      <c r="BG62" t="s">
+        <v>93</v>
+      </c>
+      <c r="BH62" t="s">
+        <v>93</v>
+      </c>
+      <c r="BI62" t="s">
+        <v>93</v>
+      </c>
+      <c r="BJ62" t="s">
+        <v>93</v>
+      </c>
+      <c r="BK62" t="s">
+        <v>93</v>
+      </c>
+      <c r="BL62" t="s">
+        <v>93</v>
+      </c>
+      <c r="BM62" t="s">
+        <v>93</v>
+      </c>
+      <c r="BN62" t="s">
+        <v>93</v>
+      </c>
+      <c r="BO62" t="s">
+        <v>93</v>
+      </c>
+      <c r="BP62" t="s">
+        <v>93</v>
+      </c>
+      <c r="BQ62" t="s">
+        <v>93</v>
+      </c>
+      <c r="BR62" t="s">
         <v>93</v>
       </c>
     </row>
